--- a/admin-surveys/views/pages/infanswers/actions/answers.xlsx
+++ b/admin-surveys/views/pages/infanswers/actions/answers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="13">
   <si>
     <t>INFORME DE POSTULANTES APROBADOS PARA CONTRATACION</t>
   </si>
@@ -23,46 +23,37 @@
     <t>NOMBRE DEL ENCUESTADO</t>
   </si>
   <si>
-    <t>PREGUNTA TIPO OPCION</t>
-  </si>
-  <si>
-    <t>NUEVA</t>
-  </si>
-  <si>
-    <t>TIENE TRABAJO</t>
-  </si>
-  <si>
-    <t>TIENE CARRO</t>
-  </si>
-  <si>
-    <t>prueba</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>dfddf</t>
+    <t>DIRECCION</t>
+  </si>
+  <si>
+    <t>PERSONAS</t>
+  </si>
+  <si>
+    <t>CAPACIDAD</t>
+  </si>
+  <si>
+    <t>JUANA MARIA</t>
+  </si>
+  <si>
+    <t>SI TIENE</t>
+  </si>
+  <si>
+    <t>2 a 3</t>
+  </si>
+  <si>
+    <t>11, 22, 33</t>
+  </si>
+  <si>
+    <t>PEDRO PEREZ</t>
   </si>
   <si>
     <t>no tiene</t>
   </si>
   <si>
-    <t>NO TENGO</t>
-  </si>
-  <si>
-    <t>osvaldo villalobos</t>
-  </si>
-  <si>
-    <t>otro</t>
-  </si>
-  <si>
-    <t>esta es una nueva encuesta</t>
-  </si>
-  <si>
-    <t>si tiene,no tiene</t>
-  </si>
-  <si>
-    <t>LO VOY A COMPRAR</t>
+    <t>3 a 4</t>
+  </si>
+  <si>
+    <t>15, 16, 17</t>
   </si>
 </sst>
 </file>
@@ -435,9 +426,7 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -448,41 +437,35 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/admin-surveys/views/pages/infanswers/actions/answers.xlsx
+++ b/admin-surveys/views/pages/infanswers/actions/answers.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
   <si>
     <t>INFORME DE POSTULANTES APROBADOS PARA CONTRATACION</t>
   </si>
@@ -23,37 +23,124 @@
     <t>NOMBRE DEL ENCUESTADO</t>
   </si>
   <si>
+    <t>NUMERO MATRICULA</t>
+  </si>
+  <si>
+    <t>NOMBRE DEL BARRIO</t>
+  </si>
+  <si>
     <t>DIRECCION</t>
   </si>
   <si>
-    <t>PERSONAS</t>
-  </si>
-  <si>
-    <t>CAPACIDAD</t>
-  </si>
-  <si>
-    <t>JUANA MARIA</t>
-  </si>
-  <si>
-    <t>SI TIENE</t>
-  </si>
-  <si>
-    <t>2 a 3</t>
-  </si>
-  <si>
-    <t>11, 22, 33</t>
-  </si>
-  <si>
-    <t>PEDRO PEREZ</t>
-  </si>
-  <si>
-    <t>no tiene</t>
-  </si>
-  <si>
-    <t>3 a 4</t>
-  </si>
-  <si>
-    <t>15, 16, 17</t>
+    <t>NUMERO DE TELEFONO</t>
+  </si>
+  <si>
+    <t>CORREO ELECTRONICO</t>
+  </si>
+  <si>
+    <t>UBICACION - LATITUD</t>
+  </si>
+  <si>
+    <t>UBICACION - LONGITUD</t>
+  </si>
+  <si>
+    <t>CUANTAS PERSONAS RESIDEN EN EL HOGAR</t>
+  </si>
+  <si>
+    <t>NIVEL SOCIO ECONOMICO</t>
+  </si>
+  <si>
+    <t>FRECUENCIA DEL SERVICIO</t>
+  </si>
+  <si>
+    <t>CUENTA CON SISTEMA DE ALMACENAMIENTO</t>
+  </si>
+  <si>
+    <t>EN CASO AFIRMATIVO - ESCOJA EL TIPO</t>
+  </si>
+  <si>
+    <t>CAPACIDAD DE ALMACENAMIENTO</t>
+  </si>
+  <si>
+    <t>CANTIDAD DE PUNTOS HIDRAULICOS</t>
+  </si>
+  <si>
+    <t>EN QUE TIPO DE VIVIENDA RESIDE</t>
+  </si>
+  <si>
+    <t>TAMAÑO DEL INMUEBLE EN M2</t>
+  </si>
+  <si>
+    <t>NUMERO DE HABITACIONES</t>
+  </si>
+  <si>
+    <t>NUMERO DE BAÑOS</t>
+  </si>
+  <si>
+    <t>POSEE AREAS VERDES COMO ANTEJARDIN O PATIO</t>
+  </si>
+  <si>
+    <t>USO DEL INMUEBLE</t>
+  </si>
+  <si>
+    <t>ESTA DE ACUERDO CON QUE SE LE INSTALE MEDIDOR</t>
+  </si>
+  <si>
+    <t>ROPERO ORFELIA</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CL 28 31 62</t>
+  </si>
+  <si>
+    <t>2 A 3</t>
+  </si>
+  <si>
+    <t>estrato 1</t>
+  </si>
+  <si>
+    <t>una vez a la semana</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.20, 1.20, </t>
+  </si>
+  <si>
+    <t>CASA UNIFAMILIAR</t>
+  </si>
+  <si>
+    <t>DOS</t>
+  </si>
+  <si>
+    <t>UNO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO, , </t>
+  </si>
+  <si>
+    <t>COMERCIAL</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>BURGOS JOAQUIN</t>
+  </si>
+  <si>
+    <t>CL 2 31 18</t>
+  </si>
+  <si>
+    <t>TANQUE ELEVADO</t>
+  </si>
+  <si>
+    <t>TRES</t>
   </si>
 </sst>
 </file>
@@ -405,15 +492,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -426,46 +513,194 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:22">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
+        <v>23</v>
+      </c>
+      <c r="B3">
+        <v>20996</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" t="s">
+        <v>35</v>
+      </c>
+      <c r="U3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V3" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+        <v>38</v>
+      </c>
+      <c r="B4">
+        <v>7563</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4">
+        <v>4</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/admin-surveys/views/pages/infanswers/actions/answers.xlsx
+++ b/admin-surveys/views/pages/infanswers/actions/answers.xlsx
@@ -15,11 +15,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>INFORME DE POSTULANTES APROBADOS PARA CONTRATACION</t>
   </si>
   <si>
+    <t>No. ENUCUESTA</t>
+  </si>
+  <si>
     <t>NOMBRE DEL ENCUESTADO</t>
   </si>
   <si>
@@ -86,61 +89,52 @@
     <t>ESTA DE ACUERDO CON QUE SE LE INSTALE MEDIDOR</t>
   </si>
   <si>
-    <t>ROPERO ORFELIA</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>CL 28 31 62</t>
-  </si>
-  <si>
-    <t>2 A 3</t>
-  </si>
-  <si>
-    <t>estrato 1</t>
+    <t>osvaldo</t>
+  </si>
+  <si>
+    <t>barr</t>
+  </si>
+  <si>
+    <t>ca</t>
+  </si>
+  <si>
+    <t>osvicor@hotmail.com</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>estrato 2</t>
   </si>
   <si>
     <t>una vez a la semana</t>
   </si>
   <si>
-    <t>si</t>
-  </si>
-  <si>
-    <t>OTROS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.20, 1.20, </t>
-  </si>
-  <si>
-    <t>CASA UNIFAMILIAR</t>
-  </si>
-  <si>
-    <t>DOS</t>
+    <t>4 A 5</t>
+  </si>
+  <si>
+    <t>TANQUE ELEVADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 2, </t>
+  </si>
+  <si>
+    <t>APARTAMENTO</t>
+  </si>
+  <si>
+    <t>TRES</t>
   </si>
   <si>
     <t>UNO</t>
   </si>
   <si>
-    <t xml:space="preserve">NO, , </t>
+    <t xml:space="preserve">no, , </t>
   </si>
   <si>
     <t>COMERCIAL</t>
   </si>
   <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>BURGOS JOAQUIN</t>
-  </si>
-  <si>
-    <t>CL 2 31 18</t>
-  </si>
-  <si>
-    <t>TANQUE ELEVADO</t>
-  </si>
-  <si>
-    <t>TRES</t>
+    <t>NO</t>
   </si>
 </sst>
 </file>
@@ -492,15 +486,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -567,135 +561,79 @@
       <c r="V2" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="W2" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:22">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
-        <v>20996</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="3" spans="1:23">
+      <c r="A3">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
         <v>26</v>
       </c>
+      <c r="F3">
+        <v>55</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>33</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
       <c r="J3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3">
-        <v>4</v>
-      </c>
-      <c r="P3" t="s">
         <v>32</v>
       </c>
-      <c r="R3" t="s">
+      <c r="O3" t="s">
         <v>33</v>
       </c>
+      <c r="P3">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>34</v>
+      </c>
+      <c r="R3">
+        <v>77</v>
+      </c>
       <c r="S3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" t="s">
         <v>38</v>
       </c>
-      <c r="B4">
-        <v>7563</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="W3" t="s">
         <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4">
-        <v>4</v>
-      </c>
-      <c r="P4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>24</v>
-      </c>
-      <c r="R4" t="s">
-        <v>41</v>
-      </c>
-      <c r="S4" t="s">
-        <v>34</v>
-      </c>
-      <c r="T4" t="s">
-        <v>35</v>
-      </c>
-      <c r="U4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/admin-surveys/views/pages/infanswers/actions/answers.xlsx
+++ b/admin-surveys/views/pages/infanswers/actions/answers.xlsx
@@ -15,126 +15,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
-  <si>
-    <t>INFORME DE POSTULANTES APROBADOS PARA CONTRATACION</t>
-  </si>
-  <si>
-    <t>No. ENUCUESTA</t>
-  </si>
-  <si>
-    <t>NOMBRE DEL ENCUESTADO</t>
-  </si>
-  <si>
-    <t>NUMERO MATRICULA</t>
-  </si>
-  <si>
-    <t>NOMBRE DEL BARRIO</t>
-  </si>
-  <si>
-    <t>DIRECCION</t>
-  </si>
-  <si>
-    <t>NUMERO DE TELEFONO</t>
-  </si>
-  <si>
-    <t>CORREO ELECTRONICO</t>
-  </si>
-  <si>
-    <t>UBICACION - LATITUD</t>
-  </si>
-  <si>
-    <t>UBICACION - LONGITUD</t>
-  </si>
-  <si>
-    <t>CUANTAS PERSONAS RESIDEN EN EL HOGAR</t>
-  </si>
-  <si>
-    <t>NIVEL SOCIO ECONOMICO</t>
-  </si>
-  <si>
-    <t>FRECUENCIA DEL SERVICIO</t>
-  </si>
-  <si>
-    <t>CUENTA CON SISTEMA DE ALMACENAMIENTO</t>
-  </si>
-  <si>
-    <t>EN CASO AFIRMATIVO - ESCOJA EL TIPO</t>
-  </si>
-  <si>
-    <t>CAPACIDAD DE ALMACENAMIENTO</t>
-  </si>
-  <si>
-    <t>CANTIDAD DE PUNTOS HIDRAULICOS</t>
-  </si>
-  <si>
-    <t>EN QUE TIPO DE VIVIENDA RESIDE</t>
-  </si>
-  <si>
-    <t>TAMAÑO DEL INMUEBLE EN M2</t>
-  </si>
-  <si>
-    <t>NUMERO DE HABITACIONES</t>
-  </si>
-  <si>
-    <t>NUMERO DE BAÑOS</t>
-  </si>
-  <si>
-    <t>POSEE AREAS VERDES COMO ANTEJARDIN O PATIO</t>
-  </si>
-  <si>
-    <t>USO DEL INMUEBLE</t>
-  </si>
-  <si>
-    <t>ESTA DE ACUERDO CON QUE SE LE INSTALE MEDIDOR</t>
-  </si>
-  <si>
-    <t>osvaldo</t>
-  </si>
-  <si>
-    <t>barr</t>
-  </si>
-  <si>
-    <t>ca</t>
-  </si>
-  <si>
-    <t>osvicor@hotmail.com</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>estrato 2</t>
-  </si>
-  <si>
-    <t>una vez a la semana</t>
-  </si>
-  <si>
-    <t>4 A 5</t>
-  </si>
-  <si>
-    <t>TANQUE ELEVADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1, 2, </t>
-  </si>
-  <si>
-    <t>APARTAMENTO</t>
-  </si>
-  <si>
-    <t>TRES</t>
-  </si>
-  <si>
-    <t>UNO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no, , </t>
-  </si>
-  <si>
-    <t>COMERCIAL</t>
-  </si>
-  <si>
-    <t>NO</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
+  <si>
+    <t>INFORME DE ENCUESTAS REALIZADAS</t>
+  </si>
+  <si>
+    <t>SECUENCIA</t>
+  </si>
+  <si>
+    <t>NOMBNRE</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>CUANTOS CUARTOS</t>
+  </si>
+  <si>
+    <t>MEDIDAS</t>
+  </si>
+  <si>
+    <t>JUAN MARIA</t>
+  </si>
+  <si>
+    <t>2025-12-30</t>
+  </si>
+  <si>
+    <t>otro (PRUEBA)</t>
+  </si>
+  <si>
+    <t>8, 7, 3</t>
   </si>
 </sst>
 </file>
@@ -486,15 +396,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -510,135 +420,34 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="D3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="E3" t="s">
         <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23">
-      <c r="A3">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3">
-        <v>55</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
-        <v>33</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3">
-        <v>6</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>34</v>
-      </c>
-      <c r="R3">
-        <v>77</v>
-      </c>
-      <c r="S3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>37</v>
-      </c>
-      <c r="V3" t="s">
-        <v>38</v>
-      </c>
-      <c r="W3" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
-    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
